--- a/data/seed/portfolio/L-2025-3502/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3502/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,42 +535,42 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>26789000</v>
+        <v>13227000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №135/6 от 02.07.2026</t>
+          <t>Предоплата за товар по договору №297/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>229589000</v>
+        <v>216027000</v>
       </c>
     </row>
     <row r="9">
@@ -582,61 +582,61 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>21892000</v>
+        <v>22067000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6698 за поставленный товар</t>
+          <t>Оплата по с/ф №5705 за поставленный товар</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>251481000</v>
+        <v>238094000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>36185000</v>
+        <v>5104000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>300987657</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000153182092001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,131 +646,131 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8411 за поставленный товар</t>
+          <t>Оплата по счет-факуре №7502 за поставленный товар</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>287666000</v>
+        <v>243198000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>27390000</v>
+        <v>1999000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №140/26 от 06.07.2026</t>
+          <t>Оплата за продукцию по договору №98/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>315056000</v>
+        <v>245197000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>5165000</v>
+        <v>30882000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №132/26 от 06.07.2026</t>
+          <t>Оплата по с/ф №343 за поставленный товар</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>320221000</v>
+        <v>276079000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>3480000</v>
+        <v>13249000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chirchiq Avto Ehtiyot MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>287850339</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000021420782001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №280/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №1052 за поставленный товар</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>323701000</v>
+        <v>289328000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>3120000</v>
+        <v>3920000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Andijon Qurilish XK</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>341353609</t>
+          <t>300987657</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000503320512001</t>
+          <t>20208000153182092001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №183/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №51/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>326821000</v>
+        <v>293248000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>3081000</v>
+        <v>3214000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №271/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №1590 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>329902000</v>
+        <v>296462000</v>
       </c>
     </row>
     <row r="16">
@@ -862,35 +862,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>2513000</v>
+        <v>1722000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4834 06.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>332415000</v>
+        <v>298184000</v>
       </c>
     </row>
     <row r="17">
@@ -902,35 +902,35 @@
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>2399000</v>
+        <v>1437000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №207/26 от 06.07.2026</t>
+          <t>Предоплата за товар по договору №239/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>334814000</v>
+        <v>299621000</v>
       </c>
     </row>
     <row r="18">
@@ -941,36 +941,31 @@
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10478000</v>
+        <v>20135000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>244140397</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №61/26</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>324336000</v>
+        <v>279486000</v>
       </c>
     </row>
     <row r="19">
@@ -981,71 +976,76 @@
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>11053000</v>
+        <v>63384000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Zarafshon Poligraf AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №595</t>
+          <t>Предоплата за материалы по договору №54/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>313283000</v>
+        <v>216102000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>20135000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>2340000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Oydin Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №2536</t>
+          <t>Оплата по счет-фактуре №2251 за поставленный товар</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>293148000</v>
+        <v>218442000</v>
       </c>
     </row>
     <row r="21">
@@ -1061,57 +1061,57 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>247854377</t>
+          <t>263191760</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000636244882001</t>
+          <t>20208000450343281001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №65/23</t>
+          <t>Аренда помещения за июль, дог. №29/24</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>290705000</v>
+        <v>215999000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>77197000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>6572000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,11 +1121,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №117/26 от 08.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>213508000</v>
+        <v>222571000</v>
       </c>
     </row>
     <row r="23">
@@ -1137,21 +1137,21 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>7941000</v>
+        <v>5209000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,117 +1161,117 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №318 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4547 за поставленный товар</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>221449000</v>
+        <v>227780000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>2119000</v>
+        <v>3915000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №66/26 от 09.07.2026</t>
+          <t>Оплата за товар по с/ф №8424 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>223568000</v>
+        <v>231695000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>5014000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>34802000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>300987657</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000153182092001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №3/26</t>
+          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>218554000</v>
+        <v>266497000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>30599000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>6041000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №62/26</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №132/26, НДС 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>187955000</v>
+        <v>272538000</v>
       </c>
     </row>
     <row r="27">
@@ -1297,35 +1297,35 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>10596000</v>
+        <v>3355000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8593 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №55/26, QQS 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>198551000</v>
+        <v>275893000</v>
       </c>
     </row>
     <row r="28">
@@ -1335,23 +1335,23 @@
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>12452000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>2331000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1361,251 +1361,251 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4396</t>
+          <t>Mahsulot uchun to'lov, shartnoma №33/26, QQS 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>186099000</v>
+        <v>278224000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>2410000</v>
+        <v>1988000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №156/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>188509000</v>
+        <v>280212000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>2746000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>1409000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №7321 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>185763000</v>
+        <v>281621000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2746000</v>
+        <v>12425000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Metall XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>388904718</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000133780143001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyu 2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №5085</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>183017000</v>
+        <v>269196000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>3614000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>2209000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4588</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2241</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>179403000</v>
+        <v>271405000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>37313000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>2746000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5258 за поставленный товар</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>216716000</v>
+        <v>268659000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>5573000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>2746000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4943 за поставленный товар</t>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I IYUN 2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>222289000</v>
+        <v>265913000</v>
       </c>
     </row>
     <row r="35">
@@ -1615,37 +1615,37 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>9984000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>46361000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Zarafshon Poligraf AJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Shartnoma №52/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №1/26</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>232273000</v>
+        <v>219552000</v>
       </c>
     </row>
     <row r="36">
@@ -1657,21 +1657,21 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>8616000</v>
+        <v>2636000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1681,11 +1681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9182 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №3847 17.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>240889000</v>
+        <v>222188000</v>
       </c>
     </row>
     <row r="37">
@@ -1697,21 +1697,21 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>7270000</v>
+        <v>2610000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №47/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>248159000</v>
+        <v>224798000</v>
       </c>
     </row>
     <row r="38">
@@ -1737,101 +1737,101 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>4765000</v>
+        <v>2154000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товр по с/ф №5286 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №138/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>252924000</v>
+        <v>226952000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>8694000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>2339000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Yulduz Polimer MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>229748073</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000598021313001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №91/26</t>
+          <t>Mahsulot ucun to'lov, shartnoma №153/26, QQS 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>244230000</v>
+        <v>229291000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>17935000</v>
+        <v>43592000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1841,77 +1841,77 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №98/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2021</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>226295000</v>
+        <v>185699000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>5643000</v>
+        <v>4099000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар п договору №158/26 от 20.07.2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №123/26 ОТ 21.07.2026</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>231938000</v>
+        <v>189798000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>3726000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>4022000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1921,37 +1921,37 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №121/26</t>
+          <t>Оплата по счет-фактуре №4865 за поставленный товар</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>228212000</v>
+        <v>193820000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>5038000</v>
+        <v>8122000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1961,91 +1961,91 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №65/26</t>
+          <t>Оплата за транспортные услуги по договору №9/26</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>223174000</v>
+        <v>185698000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>7310000</v>
+        <v>5192000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4824</t>
+          <t>Оплата за продукцию по дог. №149/26, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>230484000</v>
+        <v>190890000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>6293000</v>
+        <v>1912000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1594</t>
+          <t>Оплата за продукцию по договору №225/26, НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>236777000</v>
+        <v>192802000</v>
       </c>
     </row>
     <row r="46">
@@ -2055,37 +2055,37 @@
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>4335000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>21111000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №70/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по дог. №61/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>241112000</v>
+        <v>171691000</v>
       </c>
     </row>
     <row r="47">
@@ -2095,458 +2095,458 @@
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2801000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>47559000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3696 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №84/26</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>243913000</v>
+        <v>124132000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>4026000</v>
+        <v>1527000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000737913330001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>239887000</v>
+        <v>122605000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>18939000</v>
+        <v>4151000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Samarqand Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>255476878</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000209133759001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №57/26</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>220948000</v>
+        <v>118454000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>38604000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>43300000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>281449405</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>16307000219174828417</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №83/26 от 23.07.2026</t>
+          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>259552000</v>
+        <v>75154000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>14709000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>10247000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №19/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8923 от 27.07.2026, в тч. НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>244843000</v>
+        <v>85401000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>7497000</v>
+        <v>9400000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №161/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>252340000</v>
+        <v>94801000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>43300000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>2872000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16307000219174828417</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по счет-фактуре №121 за поставленный товар</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>209040000</v>
+        <v>97673000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>9024000</v>
+        <v>29316000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>316009876</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000721531820001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №107/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8339 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>218064000</v>
+        <v>126989000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>4283000</v>
+        <v>90990000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Yulduz Polimer MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>229748073</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000598021313001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5587</t>
+          <t>Оплата по с/ф №2758 за поставленный товар</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>222347000</v>
+        <v>217979000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>1527000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>3213000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000013420988001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ ЗА ИЮЛЬ 2026 Г.</t>
+          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>220820000</v>
+        <v>221192000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>6012000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>1937000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yulduz Agro Servis MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>219067648</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000885263350001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №236/26 от 27.07.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8820 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>214808000</v>
+        <v>223129000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>30574000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>1930000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2556,272 +2556,272 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №64/26</t>
+          <t>Предоплата за товар по договору №152/26 от 29.07.2026</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>184234000</v>
+        <v>225059000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>2655000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>6806000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5366 ОТ 28.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №188/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>186889000</v>
+        <v>218253000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>13122000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>18964000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №25/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №173/26</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>200011000</v>
+        <v>199289000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>2913000</v>
+        <v>4027000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3452 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №7542 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>202924000</v>
+        <v>203316000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>2407000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gulshan Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>391333023</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000974176075001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №105/26 от 30.07.2026</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>205331000</v>
+        <v>203016000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>5834000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>3496000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №85/26</t>
+          <t>Оплата за товар по счет-фактуре №7964 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>199497000</v>
+        <v>206512000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>300000</v>
+        <v>14788000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Zarafshon Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Оплата за сырье по договору №38/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>199197000</v>
+        <v>191724000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>3220000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>5125000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Samarqand Metall MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>255476878</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000209133759001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2831,272 +2831,272 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9735</t>
+          <t>Оплата по счет-фактуре №7513 за поставленный товар</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>195977000</v>
+        <v>196849000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>5785000</v>
+        <v>20106000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>244140397</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №241/26</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>190192000</v>
+        <v>176743000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>13973000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>5751000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №156/26</t>
+          <t>Оплата за товар по счет-фактуре №2666 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>176219000</v>
+        <v>182494000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>57848000</v>
+        <v>11931000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №254/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №2979</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>118371000</v>
+        <v>170563000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>2360000</v>
+        <v>12984000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Andijon Qurilish XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>341353609</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000503320512001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №197/26, QQS 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>120731000</v>
+        <v>183547000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>20106000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>5108000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Denov Qurilish Materiallari XK</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>203032993</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000604292836001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Mahsulot uchun to'lov, shartn. №264/26, QQS 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>100625000</v>
+        <v>188655000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>7048000</v>
+        <v>4902000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №269/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №3047 за поставленный товар</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>107673000</v>
+        <v>193557000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>135921000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>3243000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3106,11 +3106,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №120/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №116/26, QQS 12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-28248000</v>
+        <v>196800000</v>
       </c>
     </row>
     <row r="73">
@@ -3120,37 +3120,37 @@
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>10723000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>2440000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>263191760</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000450343281001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7371 за поставленный товар</t>
+          <t>Аренда помещения за август, дог. №29/24</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-17525000</v>
+        <v>194360000</v>
       </c>
     </row>
     <row r="74">
@@ -3160,357 +3160,357 @@
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>6436000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>27086000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №575 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №257/26</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-11089000</v>
+        <v>167274000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>4868000</v>
+        <v>6449000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по счт-фактуре №3237 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №11/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>-6221000</v>
+        <v>173723000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>2440000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>6033000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>247854377</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000636244882001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №65/23</t>
+          <t>Предоплата за товар по договору №187/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>-8661000</v>
+        <v>179756000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>9753000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>93930000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №98/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата по счет-фактуре №9814 за поставленный товар</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>-18414000</v>
+        <v>273686000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>47263000</v>
+        <v>14646000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №278/26 от 11.08.2026</t>
+          <t>Оплата за продукцию по договору №59/26, НДС 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>28849000</v>
+        <v>288332000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>23972000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>3928000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №178/26 ОТ 13.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №9/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>4877000</v>
+        <v>292260000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>11720000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>23795000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №242/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №1881</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16597000</v>
+        <v>268465000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>145451000</v>
+        <v>5304000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4833 17.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №132/26, НДС 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>162048000</v>
+        <v>273769000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>6428000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>10523000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №686 за поставленный товар</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №9562</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>168476000</v>
+        <v>263246000</v>
       </c>
     </row>
     <row r="83">
@@ -3522,35 +3522,35 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>2357000</v>
+        <v>9994000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №184/26 от 17.08.2026</t>
+          <t>Оплата по счет-фактуре №2302 за поставленный товар</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>170833000</v>
+        <v>273240000</v>
       </c>
     </row>
     <row r="84">
@@ -3560,37 +3560,37 @@
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>2742000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>7146000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата по счет-фактуре №2536 за поставленный товар</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>168091000</v>
+        <v>280386000</v>
       </c>
     </row>
     <row r="85">
@@ -3600,37 +3600,37 @@
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>2742000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>5364000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №152/26 ОТ 17.08.2026</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>165349000</v>
+        <v>285750000</v>
       </c>
     </row>
     <row r="86">
@@ -3640,23 +3640,23 @@
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>9834000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>4063000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №216/26 от 17.08.2026, НДС 12%</t>
+          <t>Shartnoma №257/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>155515000</v>
+        <v>289813000</v>
       </c>
     </row>
     <row r="87">
@@ -3681,276 +3681,276 @@
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>14411000</v>
+        <v>2742000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5370</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>141104000</v>
+        <v>287071000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>21542000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>2742000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ziyo Tur Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>374030329</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000326042928001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №172/26, QQS 12%</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>162646000</v>
+        <v>284329000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>4696000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>13766000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №158/26 от 19.08.2026</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №226/26</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>167342000</v>
+        <v>270563000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>30195000</v>
+        <v>6785000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8528 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №195 за поставленный товар</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>197537000</v>
+        <v>277348000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>4157000</v>
+        <v>3972000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9468 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №9037 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>201694000</v>
+        <v>281320000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>9679000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>90816000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Yulduz Polimer MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>229748073</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000598021313001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4224</t>
+          <t>Оплата за продукцию по договору №20/26, НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>192015000</v>
+        <v>372136000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>4091000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>12716000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5749</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>187924000</v>
+        <v>384852000</v>
       </c>
     </row>
     <row r="94">
@@ -3962,291 +3962,296 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>2464000</v>
+        <v>3048000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Yulduz Polimer MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>229748073</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000598021313001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1160 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4477 за поставленный товар</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>190388000</v>
+        <v>387900000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1525000</v>
+        <v>4025000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000013420988001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>188863000</v>
+        <v>383875000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>43300000</v>
+        <v>6677000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
+          <t>Zarafshon Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>16307000219174828417</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Xom ashyo uchun to'lov, shartn. №57/26, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>145563000</v>
+        <v>377198000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>4314000</v>
+        <v>10878000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1303 от 27.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8709 за поставленный товар</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>149877000</v>
+        <v>388076000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>23348000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>13216000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>316009876</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000721531820001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №239/26, НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №101/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>173225000</v>
+        <v>374860000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>5561000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>43300000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>281449405</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>16307000219174828417</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №186 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>178786000</v>
+        <v>331560000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>300000</v>
+        <v>1525000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000737913330001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>178486000</v>
+        <v>330035000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>15087000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>18885000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Zarafshon Poligraf AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>316009876</t>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000721531820001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4256,182 +4261,182 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2518 от 01.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №3244</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>193573000</v>
+        <v>311150000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>6441000</v>
+        <v>3171000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №108/26 от 03.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №6814 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>200014000</v>
+        <v>314321000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>3516000</v>
+        <v>6839000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №22/26</t>
+          <t>Оплата за транспортные услуги по договору №127/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>196498000</v>
+        <v>307482000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>2591000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>3314000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>247854377</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000636244882001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №65/23</t>
+          <t>Предоплата за товар по дог. №4/26 от 31.08.2026</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>193907000</v>
+        <v>310796000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>14419000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>3292000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8778</t>
+          <t>Оплата за продукцию по договору №120/26, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>179488000</v>
+        <v>314088000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>21355000</v>
+        <v>300000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
@@ -4451,797 +4456,792 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>158133000</v>
+        <v>313788000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>74409000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8729 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5157</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>232542000</v>
+        <v>293988000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>51043000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>21381000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №210/26 от 10.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №1278</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>283585000</v>
+        <v>272607000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>17158000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>25624000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №5779</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>300743000</v>
+        <v>246983000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>3461000</v>
+        <v>28497000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Zarafshon Poligraf AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №18/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №9479</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>297282000</v>
+        <v>218486000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46275</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>10179000</v>
+        <v>29988000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4306</t>
+          <t>Предоплата за материалы по договору №104/26</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>287103000</v>
+        <v>188498000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>18423000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>6746000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №67/26 от 10.09.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №191/26 от 01.09.2026</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>268680000</v>
+        <v>195244000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>4389000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>8108000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8708</t>
+          <t>Предоплата за товар по дог. №60/26 от 03.09.2026</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>264291000</v>
+        <v>203352000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>28664000</v>
+        <v>2545000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>316009876</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000721531820001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №202/26 от 14.09.2026</t>
+          <t>Shartnoma №128/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>292955000</v>
+        <v>205897000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>14803000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>4497000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barakali Avto Ehtiyot MChJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>302297480</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000355980213001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4897 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №22/26</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>307758000</v>
+        <v>201400000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>13257000</v>
+        <v>20190000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №265/26 от 14.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №8463 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>321015000</v>
+        <v>221590000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>6873000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>21355000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>353162786</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shartnoma №140/26 bo'yicha oldindan to'lov</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>327888000</v>
+        <v>200235000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>8740000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>8218000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2047</t>
+          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>319148000</v>
+        <v>208453000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>9805000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>3657000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №221/26</t>
+          <t>Оплата по счет-фактуре №4502 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>309343000</v>
+        <v>212110000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>13065000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>2365000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №130/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №63/26, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>296278000</v>
+        <v>214475000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>14648000</v>
+        <v>10915000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №22/26 ОТ 15.09.2026</t>
+          <t>Оплата за продукцию по договору №234/26, НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>310926000</v>
+        <v>225390000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>3215000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>3240000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5355</t>
+          <t>Оплата по с/ф №3650 за поставленный товар</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>307711000</v>
+        <v>228630000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>7008000</v>
+        <v>2591000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>263191760</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000450343281001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8858</t>
+          <t>Аренда помещения за сентябрь, дог. №29/24</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>300703000</v>
+        <v>226039000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46281</v>
+        <v>46274</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>2912000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>22823000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата по счет-фактуре №3859 за поставленный товар</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>297791000</v>
+        <v>248862000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>2912000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>37637000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Polimer MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>229748073</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000598021313001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Предоплата за товар по дог. №269/26 от 10.09.2026</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>294879000</v>
+        <v>286499000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>3363000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>3900000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5251,77 +5251,77 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №269/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7247</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>291516000</v>
+        <v>290399000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>7549000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>27823000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Farovon Poligraf MChJ</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>379889047</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000841337801001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по догоору №292/26 от 18.09.2026</t>
+          <t>Оплата за сырье по договору №67/26 от 10.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>299065000</v>
+        <v>262576000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>96303000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>20391000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Samarqand Metall MChJ</t>
+          <t>Nukus Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>255476878</t>
+          <t>216278600</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000209133759001</t>
+          <t>20208000474088461001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5331,182 +5331,182 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №103</t>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>202762000</v>
+        <v>282967000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>44354000</v>
+        <v>8498000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6228 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5295</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>247116000</v>
+        <v>291465000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>24767000</v>
+        <v>4596000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6935 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №8573 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>271883000</v>
+        <v>296061000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>7534000</v>
+        <v>4511000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Andijon Poligraf XK</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>353162786</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000004740884001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №233/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3897 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>279417000</v>
+        <v>300572000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>3308000</v>
+        <v>2912000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №963</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>276109000</v>
+        <v>297660000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>4459000</v>
+        <v>2912000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
@@ -5531,157 +5531,157 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>271650000</v>
+        <v>294748000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>5033000</v>
+        <v>8417000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1313</t>
+          <t>Оплата за товары согласно счет-фактуре №5355</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>266617000</v>
+        <v>286331000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>15978000</v>
+        <v>9340000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №187/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>282595000</v>
+        <v>295671000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>1620000</v>
+        <v>42409000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ilhom Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>306901351</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000013420988001</t>
+          <t>20208000182937569001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Оплата за транспортные услуги по договору №269/26</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>280975000</v>
+        <v>253262000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>4731000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>13757000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Samarqand Metall MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>255476878</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000209133759001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5691,352 +5691,357 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4053</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7009 ОТ 18.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>276244000</v>
+        <v>267019000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>43300000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>14578000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
+          <t>Denov Qurilish Materiallari XK</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>203032993</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>16307000219174828417</t>
+          <t>20208000604292836001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за продукцию по договору №287/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>232944000</v>
+        <v>281597000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>17306000</v>
+        <v>5348000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Oqtosh Non MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>316009876</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000721531820001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5689 ОТ 28.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Shartnoma №299/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>250250000</v>
+        <v>286945000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>6148000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>100665000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Durdona Non MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>215657484</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000484165307001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3493 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №8708</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>256398000</v>
+        <v>186280000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>8299000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>3553000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Toshkent Non MChJ</t>
+          <t>Guliston Yog'och MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>379642436</t>
+          <t>235360905</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000954958624001</t>
+          <t>20208000332051220001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №106/26</t>
+          <t>Оплата за товар по счет-фактуре №1050 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>248099000</v>
+        <v>189833000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>18345000</v>
+        <v>4306000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №716</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>229754000</v>
+        <v>185527000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>25333000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>6550000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bahor Agro MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>244140397</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000778345581001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №158/26</t>
+          <t>Оплата за товарпо счет-фактуре №8842 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>204421000</v>
+        <v>192077000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>5537000</v>
+        <v>2475000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ziyo Un Mahsulotlari MChJ</t>
+          <t>Oydin Logistik AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>281449405</t>
+          <t>244940525</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000583718517001</t>
+          <t>20208000371851786001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8418 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №88/26, QQS 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>209958000</v>
+        <v>194552000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>3645000</v>
+        <v>1620000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Yulduz Agro Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>219067648</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000885263350001</t>
+          <t>20208000737913330001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №138/26 от 29.09.2026, НДС 12%</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>206313000</v>
+        <v>192932000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>10813000</v>
+        <v>5100000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Qo'qon Qurilish Materiallari AJ</t>
+          <t>Zarafshon Poligraf AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>330538009</t>
+          <t>312103546</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000696148781001</t>
+          <t>20208000023547784001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6046,71 +6051,746 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №288/26 от 29.09.2026, НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №4519</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>195500000</v>
+        <v>187832000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>300000</v>
+        <v>5330000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
+          <t>Durdona Non MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>215657484</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000484165307001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №1816</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>182502000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B148" t="n">
+        <v>240</v>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>34564000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Namangan Metall XK</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>388904718</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000133780143001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №4053</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>147938000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B149" t="n">
+        <v>241</v>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>10769000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Nukus Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>216278600</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000474088461001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>158707000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>43300000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3502)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>16307000219174828417</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2025-3502 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>115407000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B151" t="n">
+        <v>243</v>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>33268000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Guliston Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>235360905</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000332051220001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №22/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>148675000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B152" t="n">
+        <v>244</v>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>21932000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Oydin Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>244940525</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000371851786001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №273/26 ОТ 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>170607000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B153" t="n">
+        <v>245</v>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>5517000</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Nukus Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>216278600</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000474088461001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №68/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>176124000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B154" t="n">
+        <v>246</v>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>4912000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Guliston Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>235360905</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000332051220001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №6709 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>181036000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B155" t="n">
+        <v>247</v>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>3699000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Oydin Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>244940525</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000371851786001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №237/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>184735000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B156" t="n">
+        <v>248</v>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>3516000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Oydin Logistik AJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>244940525</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000371851786001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №5/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>188251000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>6649000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Ilhom Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>306901351</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000182937569001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №158/26</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>181602000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>10722000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Ilhom Qog'oz MChJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>306901351</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000182937569001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №75/26</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>170880000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>14554000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Durdona Non MChJ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>215657484</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000484165307001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата за сырье по договору №288/26 от 29.09.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>156326000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>23430000</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Guliston Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>235360905</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000332051220001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №1301 от 30.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>179756000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>21761000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Yulduz Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>229748073</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000598021313001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>201517000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>6054000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Yulduz Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>229748073</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000598021313001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №8920 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>207571000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>Yangi Asr Bank</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>01089</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>КОМИССИЯБАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА СЕНТЯБРЬ</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>207271000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>12071000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Durdona Non MChJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>215657484</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000484165307001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov hf №5336</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
         <v>195200000</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
-        <v>1055575000</v>
-      </c>
-      <c r="D148" s="4" t="n">
-        <v>1047975000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="C165" s="4" t="n">
+        <v>1047745000</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>1040145000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C166" s="4" t="n">
         <v>195200000</v>
       </c>
-      <c r="D149" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
